--- a/Cloud_Region_Data.xlsx
+++ b/Cloud_Region_Data.xlsx
@@ -144,10 +144,10 @@
     <xf numFmtId="166" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
       <alignment vertical="center" horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
+      <alignment vertical="center" horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
-      <alignment vertical="center" horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true" applyNumberFormat="true">
       <alignment vertical="center" horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true">
@@ -254,29 +254,29 @@
         <v>0.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>32.0</v>
+        <v>53.0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>12.0</v>
+        <v>28.0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.375</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="4" t="n">
-        <v>440.0</v>
+        <v>487.0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>210.0</v>
+        <v>237.0</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.486652977412731</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-0.10227272727272728</v>
+        <v>0.04164890937972182</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-1374.5454545454547</v>
+        <v>927.1047227926077</v>
       </c>
     </row>
     <row r="3">
@@ -292,7 +292,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
@@ -311,19 +311,19 @@
         <v>0.7</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>47.0</v>
+        <v>35.0</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>28.0</v>
+        <v>19.0</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="L3" s="10" t="n">
-        <v>0.4042553191489362</v>
+        <v>0.45714285714285713</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>169.7872340425532</v>
+        <v>192.00000000000003</v>
       </c>
     </row>
     <row r="4">
@@ -339,17 +339,17 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>莆田城厢万达</t>
+          <t>泉州洛江</t>
         </is>
       </c>
       <c r="D4" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G4" s="14" t="n">
         <v>1.0</v>
@@ -358,19 +358,19 @@
         <v>0.7</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="K4" s="14" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="L4" s="14" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>420.0</v>
+        <v>268.8</v>
       </c>
     </row>
     <row r="5">
@@ -386,38 +386,38 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>福州万象城</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.75</v>
+        <v>1.0</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>34.0</v>
+        <v>11.0</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>18.0</v>
+        <v>9.0</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>0.22058823529411764</v>
+        <v>0.18181818181818177</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>370.5882352941176</v>
+        <v>76.36363636363635</v>
       </c>
     </row>
     <row r="6">
@@ -433,38 +433,38 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>福州东二环泰禾</t>
+          <t>福州榕泰</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E6" s="13" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F6" s="13" t="n">
         <v>3.0</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>2.0</v>
-      </c>
       <c r="G6" s="14" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.75</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>0.36666666666666664</v>
+        <v>0.45</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>30.0</v>
+        <v>35.0</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>12.0</v>
+        <v>16.0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.4</v>
+        <v>0.45714285714285713</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.29285714285714287</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>335.99999999999994</v>
+        <v>492.0</v>
       </c>
     </row>
     <row r="7">
@@ -480,38 +480,38 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>泉州鲤城</t>
+          <t>龙岩新罗物流大道</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>3.0</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.6</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0.15517241379310343</v>
+        <v>0.15</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>391.03448275862064</v>
+        <v>252.0</v>
       </c>
     </row>
     <row r="8">
@@ -527,38 +527,38 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>泉州鲤城</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0.2</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>-0.1</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>42.0</v>
+        <v>33.0</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>17.0</v>
+        <v>13.0</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0.40476190476190477</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>-0.20476190476190476</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>-429.99999999999994</v>
+        <v>687.2727272727273</v>
       </c>
     </row>
     <row r="9">
@@ -574,38 +574,38 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>25.0</v>
+        <v>55.0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>15.0</v>
+        <v>32.0</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5818181818181818</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>-0.6</v>
+        <v>-0.08181818181818178</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>-756.0</v>
+        <v>-274.9090909090908</v>
       </c>
     </row>
     <row r="10">
@@ -621,38 +621,38 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>泉州晋江</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>38.0</v>
+        <v>49.0</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>13.0</v>
+        <v>21.0</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0.34210526315789475</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>-0.34210526315789475</v>
+        <v>0.07142857142857145</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>-143.68421052631578</v>
+        <v>240.00000000000009</v>
       </c>
     </row>
     <row r="11">
@@ -668,38 +668,38 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>泉州洛江</t>
+          <t>福州仓山金林路</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>24.0</v>
+        <v>42.0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.33333333333333326</v>
+        <v>0.5</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>-0.33333333333333326</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>-140.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -715,38 +715,38 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>福州万象城</t>
+          <t>泉州晋江</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E12" s="13" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="13" t="n">
         <v>2.0</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>0.0</v>
-      </c>
       <c r="G12" s="14" t="n">
-        <v>0.0</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>-0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>11.0</v>
+        <v>43.0</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.34883720930232553</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>-0.7272727272727273</v>
+        <v>0.05116279069767443</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>-610.9090909090909</v>
+        <v>107.4418604651163</v>
       </c>
     </row>
     <row r="13">
@@ -762,38 +762,38 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>福州仓山万达</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E13" s="9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>1.0</v>
       </c>
-      <c r="F13" s="9" t="n">
-        <v>0.0</v>
-      </c>
       <c r="G13" s="10" t="n">
-        <v>0.0</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-0.3</v>
+        <v>0.033333333333333326</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>18.0</v>
+        <v>32.0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>7.0</v>
+        <v>20.0</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.38888888888888884</v>
+        <v>0.625</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-0.38888888888888884</v>
+        <v>-0.2916666666666667</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>-163.33333333333334</v>
+        <v>-367.5</v>
       </c>
     </row>
     <row r="14">
@@ -809,38 +809,38 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>福州榕泰</t>
+          <t>福州东二环泰禾</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0.0</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>-0.3</v>
+        <v>0.033333333333333326</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="J14" s="13" t="n">
         <v>13.0</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.40625</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>-0.40625</v>
+        <v>-0.06060606060606061</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>-341.25</v>
+        <v>-76.36363636363636</v>
       </c>
     </row>
     <row r="15">
@@ -856,14 +856,14 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>龙岩新罗物流大道</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.0</v>
@@ -875,19 +875,19 @@
         <v>-0.3</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.5769230769230769</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>-240.0</v>
+        <v>-484.6153846153846</v>
       </c>
     </row>
     <row r="16">
@@ -903,29 +903,39 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>厦门SM新生活广场</t>
+          <t>福州仓山万达</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
+      <c r="G16" s="14" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>-0.3</v>
+      </c>
       <c r="I16" s="13" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
+        <v>7.0</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>-0.3684210526315789</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>-154.73684210526315</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -940,7 +950,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>厦门万象城</t>
+          <t>厦门SM新生活广场</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
@@ -952,17 +962,17 @@
       <c r="F17" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
       <c r="I17" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -977,7 +987,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>厦门世茂Emall</t>
+          <t>厦门万象城</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
@@ -989,17 +999,17 @@
       <c r="F18" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
       <c r="I18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="J18" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -1014,7 +1024,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>厦门宝龙一城</t>
+          <t>厦门世茂Emall</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
@@ -1026,19 +1036,17 @@
       <c r="F19" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
       <c r="I19" s="9" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="K19" s="10" t="n">
-        <v>0.6551724137931033</v>
-      </c>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -1065,17 +1073,17 @@
       <c r="F20" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
       <c r="I20" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="J20" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -1102,17 +1110,17 @@
       <c r="F21" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
       <c r="I21" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="J21" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -1139,17 +1147,17 @@
       <c r="F22" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
       <c r="I22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="J22" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -1176,17 +1184,17 @@
       <c r="F23" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
       <c r="I23" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="J23" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -1201,7 +1209,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>福州苏宁（外展店）</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
@@ -1213,19 +1221,17 @@
       <c r="F24" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
       <c r="I24" s="13" t="n">
-        <v>36.0</v>
+        <v>0.0</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>18.0</v>
-      </c>
-      <c r="K24" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -1240,7 +1246,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>福州苏宁（外展店）</t>
+          <t>福州青口汽车城</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
@@ -1252,17 +1258,17 @@
       <c r="F25" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
       <c r="I25" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -1277,7 +1283,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>福州青口汽车城</t>
+          <t>莆田城厢万达</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
@@ -1289,17 +1295,19 @@
       <c r="F26" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
       <c r="I26" s="13" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
+        <v>12.0</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -1322,17 +1330,17 @@
       <c r="F27" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
       <c r="I27" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="J27" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -1355,17 +1363,17 @@
       <c r="F28" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
       <c r="I28" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -1392,17 +1400,17 @@
       <c r="F29" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
       <c r="I29" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="J29" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -1429,17 +1437,17 @@
       <c r="F30" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
       <c r="I30" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="J30" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -1466,17 +1474,17 @@
       <c r="F31" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
       <c r="I31" s="9" t="n">
         <v>0.0</v>
       </c>
       <c r="J31" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -1503,17 +1511,17 @@
       <c r="F32" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
       <c r="I32" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="J32" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -1540,17 +1548,17 @@
       <c r="F33" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
       <c r="I33" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="J33" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/Cloud_Region_Data.xlsx
+++ b/Cloud_Region_Data.xlsx
@@ -254,29 +254,29 @@
         <v>0.3</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>53.0</v>
+        <v>30.0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>28.0</v>
+        <v>15.0</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="4" t="n">
-        <v>487.0</v>
+        <v>512.0</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>237.0</v>
+        <v>249.0</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.486652977412731</v>
+        <v>0.486328125</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.04164890937972182</v>
+        <v>0.013671875</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>927.1047227926077</v>
+        <v>172.265625</v>
       </c>
     </row>
     <row r="3">
@@ -292,7 +292,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>莆田城厢万达</t>
         </is>
       </c>
       <c r="D3" s="8" t="n">
@@ -311,19 +311,19 @@
         <v>0.7</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>35.0</v>
+        <v>25.0</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.52</v>
       </c>
       <c r="L3" s="10" t="n">
-        <v>0.45714285714285713</v>
+        <v>0.48</v>
       </c>
       <c r="M3" s="9" t="n">
-        <v>192.00000000000003</v>
+        <v>201.6</v>
       </c>
     </row>
     <row r="4">
@@ -339,38 +339,38 @@
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>泉州洛江</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D4" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1.0</v>
+        <v>0.75</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>25.0</v>
+        <v>39.0</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>9.0</v>
+        <v>22.0</v>
       </c>
       <c r="K4" s="14" t="n">
-        <v>0.36</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="L4" s="14" t="n">
-        <v>0.64</v>
+        <v>0.1858974358974359</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>268.8</v>
+        <v>312.3076923076923</v>
       </c>
     </row>
     <row r="5">
@@ -386,38 +386,38 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>福州万象城</t>
+          <t>福州仓山金林路</t>
         </is>
       </c>
       <c r="D5" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>1.0</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>11.0</v>
+        <v>45.0</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5111111111111111</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>0.18181818181818177</v>
+        <v>0.23888888888888893</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>76.36363636363635</v>
+        <v>401.33333333333337</v>
       </c>
     </row>
     <row r="6">
@@ -433,38 +433,38 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>福州榕泰</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E6" s="13" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="F6" s="13" t="n">
         <v>4.0</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <v>3.0</v>
-      </c>
       <c r="G6" s="14" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>0.45</v>
+        <v>0.2714285714285714</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>35.0</v>
+        <v>59.0</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>16.0</v>
+        <v>34.0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.45714285714285713</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>0.29285714285714287</v>
+        <v>-0.004842615012106588</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>492.0</v>
+        <v>-14.237288135593369</v>
       </c>
     </row>
     <row r="7">
@@ -480,38 +480,38 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>龙岩新罗物流大道</t>
+          <t>泉州晋江</t>
         </is>
       </c>
       <c r="D7" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>25.0</v>
+        <v>45.0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0.6</v>
+        <v>0.35555555555555557</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0.15</v>
+        <v>0.14444444444444443</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>252.0</v>
+        <v>121.33333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -527,38 +527,38 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>泉州鲤城</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>0.36666666666666664</v>
+        <v>0.2</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>33.0</v>
+        <v>51.0</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>13.0</v>
+        <v>22.0</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.43137254901960786</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.06862745098039214</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>687.2727272727273</v>
+        <v>57.64705882352939</v>
       </c>
     </row>
     <row r="9">
@@ -574,17 +574,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>福州万象城</t>
         </is>
       </c>
       <c r="D9" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.5</v>
@@ -593,19 +593,19 @@
         <v>0.2</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>55.0</v>
+        <v>13.0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>32.0</v>
+        <v>10.0</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.5818181818181818</v>
+        <v>0.7692307692307692</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>-0.08181818181818178</v>
+        <v>-0.2692307692307693</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>-274.9090909090908</v>
+        <v>-226.1538461538462</v>
       </c>
     </row>
     <row r="10">
@@ -621,17 +621,17 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>福州榕泰</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>0.5</v>
@@ -640,19 +640,19 @@
         <v>0.2</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>49.0</v>
+        <v>37.0</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0.42857142857142855</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>0.07142857142857145</v>
+        <v>0.040540540540540515</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>240.00000000000009</v>
+        <v>34.054054054054035</v>
       </c>
     </row>
     <row r="11">
@@ -668,38 +668,38 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>泉州洛江</t>
         </is>
       </c>
       <c r="D11" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>42.0</v>
+        <v>26.0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
       <c r="K11" s="10" t="n">
-        <v>0.5</v>
+        <v>0.34615384615384615</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.0</v>
+        <v>-0.34615384615384615</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>0.0</v>
+        <v>-145.3846153846154</v>
       </c>
     </row>
     <row r="12">
@@ -715,38 +715,38 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>泉州晋江</t>
+          <t>福州东二环泰禾</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>0.4</v>
+        <v>0.0</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>43.0</v>
+        <v>36.0</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0.34883720930232553</v>
+        <v>0.36111111111111105</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>0.05116279069767443</v>
+        <v>-0.36111111111111105</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>107.4418604651163</v>
+        <v>-455.0</v>
       </c>
     </row>
     <row r="13">
@@ -762,38 +762,38 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>厦门宝龙一城</t>
+          <t>福州仓山万达</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.33333333333333326</v>
+        <v>0.0</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.033333333333333326</v>
+        <v>-0.3</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>32.0</v>
+        <v>20.0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>20.0</v>
+        <v>7.0</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>0.625</v>
+        <v>0.35</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-0.2916666666666667</v>
+        <v>-0.35</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>-367.5</v>
+        <v>-147.0</v>
       </c>
     </row>
     <row r="14">
@@ -809,38 +809,38 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>福州东二环泰禾</t>
+          <t>龙岩新罗物流大道</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0.33333333333333326</v>
+        <v>0.0</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>0.033333333333333326</v>
+        <v>-0.3</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>33.0</v>
+        <v>26.0</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>-0.06060606060606061</v>
+        <v>-0.5769230769230769</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>-76.36363636363636</v>
+        <v>-242.3076923076923</v>
       </c>
     </row>
     <row r="15">
@@ -856,39 +856,29 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>厦门SM新生活广场</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>-0.3</v>
-      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
       <c r="I15" s="9" t="n">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="K15" s="10" t="n">
-        <v>0.5769230769230769</v>
-      </c>
-      <c r="L15" s="10" t="n">
-        <v>-0.5769230769230769</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>-484.6153846153846</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -903,39 +893,29 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>福州仓山万达</t>
+          <t>厦门万象城</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F16" s="13" t="n">
         <v>0.0</v>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>-0.3</v>
-      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="13" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="K16" s="14" t="n">
-        <v>0.3684210526315789</v>
-      </c>
-      <c r="L16" s="14" t="n">
-        <v>-0.3684210526315789</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>-154.73684210526315</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -950,7 +930,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>厦门SM新生活广场</t>
+          <t>厦门世茂Emall</t>
         </is>
       </c>
       <c r="D17" s="8" t="n">
@@ -987,7 +967,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>厦门万象城</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
@@ -1002,12 +982,14 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
       <c r="I18" s="13" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="16"/>
+        <v>20.0</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>0.6451612903225806</v>
+      </c>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
     </row>
@@ -1024,7 +1006,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>厦门世茂Emall</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D19" s="8" t="n">
@@ -1039,12 +1021,14 @@
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
       <c r="I19" s="9" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="15"/>
+        <v>15.0</v>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>0.5769230769230769</v>
+      </c>
       <c r="L19" s="15"/>
       <c r="M19" s="15"/>
     </row>
@@ -1209,7 +1193,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>福州苏宁（外展店）</t>
+          <t>泉州鲤城</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
@@ -1224,12 +1208,14 @@
       <c r="G24" s="16"/>
       <c r="H24" s="16"/>
       <c r="I24" s="13" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>13.0</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>0.3939393939393939</v>
+      </c>
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
     </row>
@@ -1246,7 +1232,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>福州青口汽车城</t>
+          <t>福州苏宁（外展店）</t>
         </is>
       </c>
       <c r="D25" s="8" t="n">
@@ -1283,7 +1269,7 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>莆田城厢万达</t>
+          <t>福州青口汽车城</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
@@ -1298,14 +1284,12 @@
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
       <c r="I26" s="13" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="K26" s="14" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="16"/>
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
     </row>
